--- a/table/tsmr.xlsx
+++ b/table/tsmr.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771817C1-BC01-C24E-8252-FB1BA43BAD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C13A3F-29A1-0348-9999-9543EEEB2B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="900" windowWidth="14020" windowHeight="18060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1040" yWindow="900" windowWidth="22860" windowHeight="18060" firstSheet="15" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="two_sample_MR" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3603" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3619" uniqueCount="592">
   <si>
     <t>MR</t>
   </si>
@@ -1940,6 +1940,9 @@
   </si>
   <si>
     <t>( -0.0531000090276692 , 0.282818444898021 )</t>
+  </si>
+  <si>
+    <t>Q/Q_df</t>
   </si>
 </sst>
 </file>
@@ -11182,7 +11185,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -11212,6 +11217,10 @@
       <c r="I28" s="36">
         <v>0.98665250000000004</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.39657552941176472</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -11240,6 +11249,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.98640859999999997</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.41053450000000002</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -11717,7 +11730,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -11747,6 +11762,10 @@
       <c r="I28" s="36">
         <v>0.99990849999999998</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.35830578947368419</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -11775,6 +11794,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99994539999999998</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.34984564102564103</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -12252,7 +12275,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -12282,6 +12307,10 @@
       <c r="I28" s="36">
         <v>0.99999930000000004</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.23419634285714289</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -12310,6 +12339,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99999950000000004</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.23250800000000002</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -12787,7 +12820,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -12817,6 +12852,10 @@
       <c r="I28" s="36">
         <v>0.93686789999999998</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.48021546153846156</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -12845,6 +12884,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.92399629999999999</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.51895635714285715</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -13323,7 +13366,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -13353,6 +13398,10 @@
       <c r="I28" s="36">
         <v>0.77893100000000004</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.59975100000000003</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -13381,6 +13430,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.85101919999999998</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.53381655555555563</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -13859,7 +13912,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -13889,6 +13944,10 @@
       <c r="I28" s="36">
         <v>0.99990840000000003</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.35833526315789471</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -13917,6 +13976,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99994539999999998</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.34987410256410256</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -14395,7 +14458,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -14425,6 +14490,10 @@
       <c r="I28" s="36">
         <v>0.9998551</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.37167342105263157</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -14453,6 +14522,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99990060000000003</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.36637076923076922</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -14931,7 +15004,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -14961,6 +15036,10 @@
       <c r="I28" s="36">
         <v>0.91212729999999997</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.58660888888888896</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -14989,6 +15068,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.88913509999999996</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.6272194736842106</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -17621,7 +17704,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -17651,6 +17736,10 @@
       <c r="I28" s="36">
         <v>0.99975919999999996</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.22265533333333332</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -17679,6 +17768,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99987510000000002</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.21497510526315788</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -29151,7 +29244,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -29181,6 +29276,10 @@
       <c r="I28" s="36">
         <v>0.99858930000000001</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.43344184210526321</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -29209,6 +29308,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99856520000000004</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.46363027027027021</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -33877,7 +33980,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -33907,6 +34012,10 @@
       <c r="I28" s="36">
         <v>0.98663999999999996</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.39664188235294118</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -33935,6 +34044,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.98639149999999998</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.41062355555555557</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -34411,7 +34524,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -34441,6 +34556,10 @@
       <c r="I28" s="36">
         <v>0.99990840000000003</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.35833526315789471</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -34469,6 +34588,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99994539999999998</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.34987410256410256</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -34947,7 +35070,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -34977,6 +35102,10 @@
       <c r="I28" s="36">
         <v>0.99999970000000005</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.22034214285714285</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -35005,6 +35134,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99999979999999999</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.22033783333333334</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -35479,7 +35612,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -35509,6 +35644,10 @@
       <c r="I28" s="36">
         <v>0.91212729999999997</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.58660888888888896</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -35537,6 +35676,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.88913509999999996</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.6272194736842106</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -36015,7 +36158,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -36045,6 +36190,10 @@
       <c r="I28" s="36">
         <v>0.99975670000000005</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.22296744444444444</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -36073,6 +36222,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99986969999999997</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.21614642105263157</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
@@ -36551,7 +36704,9 @@
       <c r="I27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="J27" s="27"/>
+      <c r="J27" s="27" t="s">
+        <v>591</v>
+      </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="32">
@@ -36581,6 +36736,10 @@
       <c r="I28" s="36">
         <v>0.99856350000000005</v>
       </c>
+      <c r="J28" s="28">
+        <f>G28/H28</f>
+        <v>0.44589729729729732</v>
+      </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="32">
@@ -36609,6 +36768,10 @@
       </c>
       <c r="I29" s="36">
         <v>0.99854540000000003</v>
+      </c>
+      <c r="J29" s="28">
+        <f>G29/H29</f>
+        <v>0.45198657894736843</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="19">
